--- a/data_extactor/batch_10_fa/trimmed/batch_0079_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0079_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | نظارت | درک مطلب | سخن گفتن | نگارش</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نظارت | درک مطلب | سخن گفتن | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | رایانه و الکترونیک | ریاضیات | ایمنی و امنیت عمومی | مکانیک | مخابرات | ترابری</t>
+          <t>مهندسی و فناوری | رایانه و الکترونیک | ریاضیات | ایمنی و امنیت عمومی | مکانیک | مخابرات | حمل و نقل</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دید نزدیک | حساسیت به مسئله | چابکی دستی | تشخیص رنگ | چابکی انگشتان | استدلال قیاسی</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | حساسیت به مسئله | مهارت دستی | تشخیص رنگ بصری | مهارت انگشتان | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنسین اویونیک و الکترونیک هوانوردی | تعمیرکار الکتروموتور، ابزار برقی و تجهیزات وابسته | کاردان فنی مهندسی برق و الکترونیک | تعمیرکار تجهیزات برقی و الکترونیکی صنعتی و تجاری | تکنسین الکترومکانیک و مکاترونیک | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | تکنسین رباتیک</t>
+          <t>تکنسین‌های اویونیک و الکترونیک پرواز | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | نظارت | یادگیری فعال | نگارش</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | مکانیک | تولید و فراوری | خدمات مشتریان و خدمات فردی | ریاضیات | مهندسی و فناوری</t>
+          <t>رایانه و الکترونیک | مکانیک | تولید و فرآوری | خدمات مشتری و شخصی | ریاضیات | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | استدلال قیاسی | ثبات دست و بازو | چابکی دستی | چابکی انگشتان</t>
+          <t>حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | استدلال قیاسی | ثبات دست و بازو | مهارت دستی | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تکنسین کالیبراسیون | نصاب و تعمیرکار شیرآلات و سیستم‌های کنترلی | تعمیرکار الکتروموتور، ابزار برقی و تجهیزات وابسته | کاردان فنی مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | تکنسین الکترومکانیک و مکاترونیک | تعمیرکار تجهیزات پزشکی</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | تعمیرکاران تجهیزات پزشکی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | سخن گفتن | شنیدن فعال | نظارت</t>
+          <t>تفکر انتقادی | درک مطلب | سخن گفتن | گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>دید نزدیک | ثبات دست و بازو | درک شفاهی | حساسیت به مسئله | درک کتبی | چابکی انگشتان | دقت کنترل</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | درک شفاهی | حساسیت به مسئله | درک کتبی | مهارت انگشتان | دقت کنترل</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تعمیرکار الکتروموتور، ابزار برقی و تجهیزات وابسته | مهندس برق | سیم‌بان و تعمیرکار خطوط انتقال و توزیع برق | کاردان فنی مهندسی برق و الکترونیک | تعمیرکار تجهیزات برقی و الکترونیکی صنعتی و تجاری | برق‌کار | دیسپاچر و توزیع‌کننده انرژی برق</t>
+          <t>تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مهندسان برق | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | برق‌کاران | دیسپچرها و توزیع‌کنندگان شبکه برق</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مکانیک | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | ریاضیات | زبان انگلیسی | مهندسی و فناوری | آموزش و پرورش</t>
+          <t>مکانیک | رایانه و الکترونیک | خدمات مشتری و شخصی | ریاضیات | زبان انگلیسی | مهندسی و فناوری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی انگشتان | دید نزدیک | تشخیص رنگ | حساسیت به مسئله | استدلال قیاسی | چابکی دستی</t>
+          <t>ثبات دست و بازو | مهارت انگشتان | بینایی نزدیک | تشخیص رنگ بصری | حساسیت به مسئله | استدلال قیاسی | مهارت دستی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>نصاب و تعمیرکار تجهیزات صوتی و تصویری | مکانیک و تکنسین خدمات خودرو | تعمیرکار رایانه، خودپرداز و ماشین‌های اداری | تعمیرکار الکتروموتور، ابزار برقی و تجهیزات وابسته | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | نصاب و تعمیرکار تجهیزات رادیویی، دکل و تلفن همراه | نصاب سیستم‌های اعلام سرقت و حریق</t>
+          <t>نصاب و تعمیرکار تجهیزات صوتی و تصویری | مکانیک و تکنسین خدمات خودرو | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | نصاب سیستم‌های اعلام سرقت و حریق</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,22 +731,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>نرم‌افزار کالیبراسیون صدا | نرم‌افزار سامانه موقعیت‌یاب جهانی GPS | نرم‌افزار Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Word</t>
+          <t>نرم‌افزار کالیبراسیون صدا | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | نرم‌افزار Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Word</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | شنیدن فعال | تفکر انتقادی</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | مخابرات | مکانیک | مهندسی و فناوری | ساختمان و سازه</t>
+          <t>رایانه و الکترونیک | خدمات مشتری و شخصی | مخابرات | مکانیک | مهندسی و فناوری | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>چابکی انگشتان | دید نزدیک | تجسم فضایی | حساسیت به مسئله | استدلال قیاسی | چابکی دستی | حساسیت شنوایی</t>
+          <t>مهارت انگشتان | بینایی نزدیک | تجسم | حساسیت به مسئله | استدلال قیاسی | مهارت دستی | حساسیت شنوایی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنسین صوت و تصویر | تکنسین پخش و فرستنده‌های رادیو و تلویزیونی | تعمیرکار دوربین و تجهیزات عکاسی | تعمیرکار رایانه، خودپرداز و ماشین‌های اداری | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | نصاب سیستم‌های اعلام سرقت و حریق | نصاب و تعمیرکار تجهیزات مخابراتی (به‌جز نصابان خطوط)</t>
+          <t>تکنسین‌های تجهیزات صوتی و تصویری | تکنسین‌های پخش و اتاق فرمان | تعمیرکاران دوربین و تجهیزات عکاسی | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | نصاب سیستم‌های اعلام سرقت و حریق | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نظارت</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | مخابرات | ساختمان و سازه | مهندسی و فناوری</t>
+          <t>ایمنی و امنیت عمومی | رایانه و الکترونیک | خدمات مشتری و شخصی | مخابرات | ساختمان و ساخت‌وساز | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | دید نزدیک | استدلال قیاسی | چابکی دستی | ثبات دست و بازو | تجسم فضایی</t>
+          <t>درک شفاهی | حساسیت به مسئله | بینایی نزدیک | استدلال قیاسی | مهارت دستی | ثبات دست و بازو | تجسم</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>نصاب و تعمیرکار تجهیزات صوتی و تصویری | کاردان فنی مهندسی برق و الکترونیک | تعمیرکار تجهیزات برقی و الکترونیکی صنعتی و تجاری | برق‌کار | مهندس حفاظت و پیشگیری از حریق | نصاب و تعمیرکار تجهیزات رادیویی، دکل و تلفن همراه | نصاب و تعمیرکار تجهیزات مخابراتی (به‌جز نصابان خطوط)</t>
+          <t>نصاب و تعمیرکار تجهیزات صوتی و تصویری | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | برق‌کاران | مهندسان پیشگیری و حفاظت از حریق | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | مهندسی و فناوری | زبان انگلیسی | ترابری | ریاضیات | رایانه و الکترونیک</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | مهندسی و فناوری | زبان انگلیسی | حمل و نقل | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | درک کتبی | مرتب‌سازی اطلاعات | چابکی دستی | چابکی انگشتان | دقت کنترل</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | درک کتبی | ترتیب‌دهی اطلاعات | مهارت دستی | مهارت انگشتان | دقت کنترل</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کاردان فنی هوافضا و عملیات پرواز | خدمه خدمات زمینی هواپیما | مونتاژکار سازه، سطوح، مهار و سیستم‌های هواپیما | تکنسین اویونیک و الکترونیک هوانوردی | مکانیک خودروهای سنگین و دیزل | مکانیک ماشین‌آلات صنعتی | مکانیک ماشین‌آلات سنگین متحرک (به‌جز موتور)</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | متصدیان خدمات زمینی و سوخت‌رسانی فرودگاهی | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌های اویونیک و الکترونیک پرواز | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | مکانیک‌های ماشین‌آلات صنعتی | مکانیک تجهیزات سنگین متحرک</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی | تولید و فراوری | ریاضیات</t>
+          <t>مکانیک | خدمات مشتری و شخصی | تولید و فرآوری | ریاضیات</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی دستی | تجسم فضایی | حساسیت به مسئله | چابکی انگشتان | دید نزدیک | تشخیص رنگ</t>
+          <t>ثبات دست و بازو | مهارت دستی | تجسم | حساسیت به مسئله | مهارت انگشتان | بینایی نزدیک | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>نصاب و تعمیرکار شیشه خودرو | مکانیک و تکنسین خدمات خودرو | مکانیک خودروهای سنگین و دیزل | متصدی و اپراتور دستگاه‌های رنگ‌کاری و پوشش‌دهی | پرداخت‌کار و سنباده‌کار دستی سطوح | آپاراتی و تعمیرکار لاستیک | رویه‌کوب و تودوزی‌کار خودرو و مبل</t>
+          <t>نصاب و تعمیرکار شیشه خودرو | مکانیک و تکنسین خدمات خودرو | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | آپاراتی و پنچرگیر و تعویض‌کار لاستیک | رویه‌کوبان و مبل‌کوبان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Workday | نرم‌افزار برآورد هزینه خسارت | نرم‌افزار ثبت اطلاعات و اسناد | نرم‌افزار Microsoft Windows</t>
+          <t>Estimating software | Microsoft Windows | نرم‌افزار ثبت سوابق | نرم‌افزار Workday</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مکانیک | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | مکانیک | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دید نزدیک | قدرت ایستایی | هماهنگی چند اندام | چابکی دستی | انعطاف‌پذیری بدنی | چابکی انگشتان | ثبات دست و بازو</t>
+          <t>بینایی نزدیک | قدرت ایستا | هماهنگی چند عضو | مهارت دستی | انعطاف‌پذیری دامنه حرکت | مهارت انگشتان | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>صافکار و نقاش خودرو | مکانیک و تکنسین خدمات خودرو | شیشه‌بر و نصاب شیشه ساختمان | پرداخت‌کار و سنباده‌کار دستی سطوح | تعمیرکار درب‌های اتوماتیک و مکانیکی | تعمیرکار واگن و خودروهای ریلی | آپاراتی و تعمیرکار لاستیک</t>
+          <t>صافکار و نقاش خودرو | مکانیک و تکنسین خدمات خودرو | شیشه‌بران و نصابان شیشه | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تعمیرکاران درب‌های مکانیکی و اتوماتیک | تعمیرکار واگن قطار | آپاراتی و پنچرگیر و تعویض‌کار لاستیک</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | مهندسی و فناوری</t>
+          <t>مکانیک | خدمات مشتری و شخصی | رایانه و الکترونیک | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | چابکی دستی | دید نزدیک | چابکی انگشتان | حساسیت به مسئله | ثبات دست و بازو | دقت کنترل</t>
+          <t>استدلال قیاسی | مهارت دستی | بینایی نزدیک | مهارت انگشتان | حساسیت به مسئله | ثبات دست و بازو | دقت کنترل</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>صافکار و نقاش خودرو | تکنسین مهندسی خودرو | مکانیک خودروهای سنگین و دیزل | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | مکانیک ماشین‌آلات صنعتی | مکانیک موتورسیکلت | آپاراتی و تعمیرکار لاستیک</t>
+          <t>صافکار و نقاش خودرو | تکنسین‌های مهندسی خودرو | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | مکانیک‌های ماشین‌آلات صنعتی | مکانیک موتورسیکلت | آپاراتی و پنچرگیر و تعویض‌کار لاستیک</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
